--- a/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35087A21-882D-4394-B1D6-705B92FC3676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{560E640A-0D9E-4218-A77A-596F6B594CDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB705863-E8F5-4BCA-900F-CE8455239D0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE8941E-C0A1-4EFF-8B35-2C0B33C71532}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50B6964E-98B5-4476-AADC-D0024D507D10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C4093AF-88B4-4328-8777-BEEC2DB56C50}"/>
 </file>